--- a/从零开始学Slots/从零开始学Slots-31-番外篇-Python模拟WaySlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-31-番外篇-Python模拟WaySlots.xlsx
@@ -6536,6 +6536,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K197" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7128,5 +7131,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M67" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-31-番外篇-Python模拟WaySlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-31-番外篇-Python模拟WaySlots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="215">
   <si>
     <r>
       <rPr>
@@ -5285,7 +5285,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5408,6 +5408,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5925,13 +5933,13 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
+      <c r="A55" s="31">
+        <v>5</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>43</v>
+      <c r="A56" s="31">
+        <v>2</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6592,8 +6600,8 @@
       <c r="F4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>160</v>
+      <c r="A5" s="32">
+        <v>10</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>1781</v>
@@ -6741,8 +6749,8 @@
       <c r="E15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>160</v>
+      <c r="A16" s="32">
+        <v>10</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>1781</v>

--- a/从零开始学Slots/从零开始学Slots-31-番外篇-Python模拟WaySlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-31-番外篇-Python模拟WaySlots.xlsx
@@ -5103,12 +5103,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -5285,7 +5286,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5415,6 +5416,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6606,7 +6615,7 @@
       <c r="B5" s="17" t="n">
         <v>1781</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="33" t="n">
         <f aca="false">B5/10000</f>
         <v>0.1781</v>
       </c>
@@ -6621,7 +6630,7 @@
       <c r="B6" s="17" t="n">
         <v>1781</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">B6/10000</f>
         <v>0.1781</v>
       </c>
@@ -6636,7 +6645,7 @@
       <c r="B7" s="17" t="n">
         <v>1781</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">B7/10000</f>
         <v>0.1781</v>
       </c>
@@ -6651,7 +6660,7 @@
       <c r="B8" s="17" t="n">
         <v>1781</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">B8/10000</f>
         <v>0.1781</v>
       </c>
@@ -6666,7 +6675,7 @@
       <c r="B9" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">B9/10000</f>
         <v>0.2</v>
       </c>
@@ -6681,7 +6690,7 @@
       <c r="B10" s="17" t="n">
         <v>175</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="33" t="n">
         <f aca="false">B10/10000</f>
         <v>0.0175</v>
       </c>
@@ -6697,7 +6706,7 @@
       <c r="B11" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="33" t="n">
         <f aca="false">B11/10000</f>
         <v>0.07</v>
       </c>
